--- a/pipeline/credit_rating/output/saigonratings_xhtn_20261007.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20261007.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17723,7 +17723,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18527,7 +18527,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19733,7 +19733,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19867,7 +19867,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20604,7 +20604,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21609,7 +21609,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21743,7 +21743,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22413,7 +22413,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22681,7 +22681,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22815,7 +22815,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S339" s="1" t="n">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S340" s="1" t="n">
@@ -23418,7 +23418,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S341" s="1" t="n">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S342" t="inlineStr"/>
@@ -23518,7 +23518,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S343" t="inlineStr"/>
@@ -23567,7 +23567,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S344" t="inlineStr"/>
@@ -23616,7 +23616,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:43</t>
+          <t>2026-10-07 15:43:47</t>
         </is>
       </c>
       <c r="S345" t="inlineStr"/>
